--- a/处理结果汇总.xlsx
+++ b/处理结果汇总.xlsx
@@ -434,7 +434,7 @@
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -468,12 +468,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>中北大学计算机学院与五寨县第一中学签约共建“芯火领航”科技教育共同体，面向县域中学生开展人工智能、机器人等科普实践，通过高校师生入校授课、组织学生进实验室等方式，打通科创育人链条，缩小城乡科技教育差距。</t>
+          <t>中北大学计算机学院与五寨县第一中学签约共建“芯火领航”科技教育共同体，通过高校师生入校授课、组织中学生进实验室等方式，为县域中学生提供人工智能、机器人等科普实践，缩小城乡科技教育差距。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>科技教育共同体, 县域中学生, 城乡科技教育差距</t>
+          <t>科技教育共同体, 县域中学生, 城乡差距</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -490,12 +490,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026世界人工智能大会将于7月17日至20日在上海召开，习近平主席将出席开幕式并发表主旨讲话。大会聚焦通用人工智能、AI安全治理、产业落地，展出国产大模型等百项前沿成果，并设青年科创分论坛，推动产业高质量发展与全球合作。</t>
+          <t>2026世界人工智能大会将于7月17日至20日在上海召开，习近平主席将出席开幕式并发表主旨讲话。大会聚焦通用人工智能、AI安全治理、产业落地，展示国产大模型等百项前沿成果，并设青年科创分论坛，推动产业高质量发展与全球合作。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>人工智能, AI安全治理, 产业落地</t>
+          <t>世界人工智能大会, 通用人工智能, AI安全治理</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -512,12 +512,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026年上半年，我国货物贸易进出口总值25.47万亿元，首次突破25万亿，同比增长16.9%。新能源汽车、光伏、AI产品出口增速领先，长三角、珠三角稳定增长，中西部增速提升。海关表示将优化通关政策助力外贸。</t>
+          <t>2026年上半年我国货物贸易进出口总值25.47万亿元，同比增长16.9%，首次突破25万亿。新能源汽车、光伏、AI产品出口领跑，长三角、珠三角稳定增长，中西部增速提升。海关将优化通关便利化政策。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>外贸, 新能源汽车, 进出口</t>
+          <t>外贸, 新能源汽车, 海关</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -534,12 +534,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2025年度国家科学技术奖励大会在北京举行，习近平总书记为陈立泉、贲德院士颁发最高科学技术奖，强调“十五五”时期是建设科技强国的关键阶段，需攻克“卡脖子”技术。本年度316个获奖项目中超七成已实现产业化应用。</t>
+          <t>2025年度国家科学技术奖励大会等四会同步在京举行，习近平为陈立泉、贲德颁发最高科技奖。陈立泉推动新能源电池国产化，贲德贡献国防雷达技术。总书记强调“十五五”关键期要攻克“卡脖子”技术，引领现代化。本年度316个项目获奖，超七成已产业化。</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>国家科学技术奖, 卡脖子技术, 科技强国</t>
+          <t>国家科学技术奖, 卡脖子技术, 产业化应用</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -556,12 +556,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2025年度国家科学技术奖励大会等多场会议在京同步举行，习近平总书记出席并为最高奖获得者陈立泉、贲德颁奖。总书记强调“十五五”时期需推进科技自立自强，攻克“卡脖子”技术。本年度316个项目获奖，超七成已产业化。</t>
+          <t>2025年度国家科学技术奖励大会等四会同步在京举行，习近平总书记出席并颁奖。陈立泉、贲德获最高科技奖。总书记强调“十五五”关键期需高水平科技自立自强，攻克“卡脖子”技术。316个项目获奖，超七成已产业化。</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>国家科学技术奖, 科技自立自强, 卡脖子技术</t>
+          <t>国家科学技术奖, 高水平科技自立自强, 陈立泉</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
